--- a/forms/trg/Formulir_TRG_fdmrg.xlsx
+++ b/forms/trg/Formulir_TRG_fdmrg.xlsx
@@ -940,7 +940,11 @@
           <t>Dr. Eng. Ir. Mukhsan Putra Hatta ST., MT.</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
@@ -1054,7 +1058,7 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborator</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
